--- a/artfynd/A 37785-2025 artfynd.xlsx
+++ b/artfynd/A 37785-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1613,6 +1613,651 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127990202</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97336</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>520253</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6525178</v>
+      </c>
+      <c r="S10" t="n">
+        <v>75</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127990119</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8439</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>520253</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6525178</v>
+      </c>
+      <c r="S11" t="n">
+        <v>75</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127990133</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>520253</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6525178</v>
+      </c>
+      <c r="S12" t="n">
+        <v>75</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127990044</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>520253</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6525178</v>
+      </c>
+      <c r="S13" t="n">
+        <v>75</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127990147</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>520253</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6525178</v>
+      </c>
+      <c r="S14" t="n">
+        <v>75</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127990173</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>520253</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6525178</v>
+      </c>
+      <c r="S15" t="n">
+        <v>75</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37785-2025 artfynd.xlsx
+++ b/artfynd/A 37785-2025 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>127990202</v>
       </c>
       <c r="B10" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>127990133</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127990147</v>
       </c>
       <c r="B14" t="n">
-        <v>57660</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>127990173</v>
       </c>
       <c r="B15" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 37785-2025 artfynd.xlsx
+++ b/artfynd/A 37785-2025 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>127990202</v>
       </c>
       <c r="B10" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37785-2025 artfynd.xlsx
+++ b/artfynd/A 37785-2025 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>127990202</v>
       </c>
       <c r="B10" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37785-2025 artfynd.xlsx
+++ b/artfynd/A 37785-2025 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>127990202</v>
       </c>
       <c r="B10" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37785-2025 artfynd.xlsx
+++ b/artfynd/A 37785-2025 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>127990202</v>
       </c>
       <c r="B10" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>127990133</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127990147</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57667</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>127990173</v>
       </c>
       <c r="B15" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 37785-2025 artfynd.xlsx
+++ b/artfynd/A 37785-2025 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>127990202</v>
       </c>
       <c r="B10" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>127990133</v>
       </c>
       <c r="B12" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127990147</v>
       </c>
       <c r="B14" t="n">
-        <v>57667</v>
+        <v>57679</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>127990173</v>
       </c>
       <c r="B15" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 37785-2025 artfynd.xlsx
+++ b/artfynd/A 37785-2025 artfynd.xlsx
@@ -1618,7 +1618,7 @@
         <v>127990202</v>
       </c>
       <c r="B10" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>127990133</v>
       </c>
       <c r="B12" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>127990147</v>
       </c>
       <c r="B14" t="n">
-        <v>57679</v>
+        <v>57683</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>127990173</v>
       </c>
       <c r="B15" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 37785-2025 artfynd.xlsx
+++ b/artfynd/A 37785-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89010295</v>
+        <v>89010192</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,13 +712,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520143.3881098996</v>
+        <v>520141</v>
       </c>
       <c r="R2" t="n">
-        <v>6525152.441593443</v>
+        <v>6525161</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,24 +745,9 @@
           <t>2020-11-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-11-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera stora kuddar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +774,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89010257</v>
+        <v>89010252</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,41 +785,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hjortmon, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520138.1746727622</v>
+        <v>520138</v>
       </c>
       <c r="R3" t="n">
-        <v>6525158.620654481</v>
+        <v>6525159</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +844,14 @@
           <t>2020-11-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-11-11</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tallstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,37 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89010432</v>
+        <v>89010429</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520162.9059866225</v>
+        <v>520163</v>
       </c>
       <c r="R4" t="n">
-        <v>6525185.12623274</v>
+        <v>6525185</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,19 +948,14 @@
           <t>2020-11-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-11-11</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,60 +982,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89010255</v>
+        <v>89010295</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hjortmon, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520138.1746727622</v>
+        <v>520143</v>
       </c>
       <c r="R5" t="n">
-        <v>6525158.620654481</v>
+        <v>6525152</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,19 +1052,14 @@
           <t>2020-11-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-11-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera stora kuddar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,55 +1086,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89010252</v>
+        <v>89327910</v>
       </c>
       <c r="B6" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>2590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hjortmon, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520138.1746727622</v>
+        <v>520143</v>
       </c>
       <c r="R6" t="n">
-        <v>6525158.620654481</v>
+        <v>6525152</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,32 +1158,18 @@
           <t>2020-11-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-11-11</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På tallstubbe</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1265,55 +1188,55 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89010192</v>
+        <v>89010255</v>
       </c>
       <c r="B7" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hjortmon, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520141.2698155377</v>
+        <v>520138</v>
       </c>
       <c r="R7" t="n">
-        <v>6525161.222739452</v>
+        <v>6525159</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1340,19 +1263,9 @@
           <t>2020-11-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-11-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,15 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89327910</v>
+        <v>127990133</v>
       </c>
       <c r="B8" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,27 +1303,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2590</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1423,13 +1335,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520143.3881098996</v>
+        <v>520253</v>
       </c>
       <c r="R8" t="n">
-        <v>6525152.441593443</v>
+        <v>6525178</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,22 +1365,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-11-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,71 +1379,70 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89010429</v>
+        <v>89010270</v>
       </c>
       <c r="B9" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>102613</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hallsberg, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520162.9059866225</v>
+        <v>520195</v>
       </c>
       <c r="R9" t="n">
-        <v>6525185.12623274</v>
+        <v>6525135</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1571,24 +1472,9 @@
           <t>2020-11-11</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-11-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127990202</v>
+        <v>127990147</v>
       </c>
       <c r="B10" t="n">
-        <v>97460</v>
+        <v>57947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,31 +1512,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>102977</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1702,7 +1588,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1721,57 +1606,55 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127990119</v>
+        <v>89010257</v>
       </c>
       <c r="B11" t="n">
-        <v>8439</v>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hjortmon, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520253</v>
+        <v>520138</v>
       </c>
       <c r="R11" t="n">
-        <v>6525178</v>
+        <v>6525159</v>
       </c>
       <c r="S11" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1795,17 +1678,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>rikligt</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,29 +1692,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127990133</v>
+        <v>127990173</v>
       </c>
       <c r="B12" t="n">
-        <v>57686</v>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1844,26 +1721,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1941,7 +1818,7 @@
         <v>127990044</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2050,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127990147</v>
+        <v>127990119</v>
       </c>
       <c r="B14" t="n">
-        <v>57683</v>
+        <v>8444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,31 +1938,32 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102977</v>
+        <v>106554</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2131,12 +2009,18 @@
           <t>2025-08-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2155,56 +2039,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127990173</v>
+        <v>89010432</v>
       </c>
       <c r="B15" t="n">
-        <v>57849</v>
+        <v>97983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hjortmon, Nrk</t>
+          <t>Hallsberg, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520253</v>
+        <v>520163</v>
       </c>
       <c r="R15" t="n">
-        <v>6525178</v>
+        <v>6525185</v>
       </c>
       <c r="S15" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,12 +2106,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2020-11-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,15 +2126,121 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127990202</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hjortmon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>520253</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6525178</v>
+      </c>
+      <c r="S16" t="n">
+        <v>75</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>Per Karlsson Linderum</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>Per Karlsson Linderum</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37785-2025 artfynd.xlsx
+++ b/artfynd/A 37785-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89010192</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89010252</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89010429</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89010295</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89327910</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89010255</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127990133</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89010270</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1603,6 +1648,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127990147</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89010257</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1812,6 +1867,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127990173</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1924,6 +1984,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127990044</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2036,6 +2101,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127990119</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2135,6 +2205,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89010432</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2241,8 +2316,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127990202</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>